--- a/docs/qa/TenantEcom-test-cases.xlsx
+++ b/docs/qa/TenantEcom-test-cases.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vendor CMS'!$A$1:$U$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Super Admin'!$A$1:$U$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defect Log'!$A$1:$M$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 from docs/qa/tools. Figures recalculate as Status cells change.</t>
+          <t>Generated 2026-10-11 from docs/qa/tools. Figures recalculate as Status cells change.</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32455,45 +32455,317 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>E2E-03-005</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>E2E-03 · Catalogue to storefront</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Quick add on a home page card</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>A card on the home page adds a single-finish product without leaving the page.</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Store selling; Home Orbit home page from `pnpm seed:home-orbit`</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Designed for modern homes: HOGDH-610</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>1. Open the home page
+2. Hover the Lotus glass door handle card (phone: tap its + button)
+3. Press Add to cart on the photo
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>"Added ✓" on the card and the header cart count goes up; the cart has one Lotus glass door handle at the price the card showed.</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr"/>
+      <c r="Q11" s="11" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr"/>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-03-catalogue.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>E2E-03-006</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>E2E-03 · Catalogue to storefront</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Quick add picker for finishes and sizes</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>A product sold in several finishes and sizes opens a picker with server prices.</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Store selling; variants generated for HOPH-504 in the product editor with stock</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Size 12 inch, finish Rose gold</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>1. Open the home page
+2. Press Quick add on the Feather pull handle card
+3. Choose 12 inch and Rose gold
+4. Add to cart
+5. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>The picker shows sizes and finish swatches, the price changes with the choice, code HOPH-504-12-INCH-ROSE-GOLD shows; "Added to your cart. View cart" and the count goes up; Esc closes it.</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr"/>
+      <c r="Q12" s="11" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr"/>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-03-catalogue.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>E2E-03-007</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>E2E-03 · Catalogue to storefront</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Menu dropdown columns from Menus</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>The header dropdown shows the columns, links and picture set on the Menus screen.</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Home Orbit menus from `pnpm seed:home-orbit`</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Door hardware: Aldrops and latches, Door handles, Door accessories</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>1. Hover Door hardware in the category bar (desktop)
+2. Press Laser-cut aldrops
+3. Owner: rename the column "Door handles" to "Handles" in Menus and save
+4. Reload the store and hover Door hardware
+5. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Three headed columns, the aldrop picture and Shop all door hardware; Laser-cut aldrops opens Aldrops filtered to the laser-cut range (4 products); after the edit the column reads "Handles".</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr"/>
+      <c r="Q13" s="11" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr"/>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Store owner</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U13" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-03-catalogue.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>E2E-04-001</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Guest COD order</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>A guest places a COD order.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Store selling; COD on; zones set</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Rahul Kulkarni, 98765 43210, rahul.k@example.com, 411045, Flat 12 Shanti Kunj, Baner Road</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>1. Open http://home-orbit.localhost:3000/products/feather-stainless-steel-pull-handle-hoph-504
 2. Check delivery for 411045
@@ -32505,266 +32777,266 @@
 8. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>"Thank you, Rahul. Your order is placed." with the order number (HOM-…), amount to pay in cash, delivery date and items; the cart is empty again.</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr"/>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
-      <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr"/>
+      <c r="Q14" s="11" t="inlineStr"/>
+      <c r="R14" s="11" t="inlineStr"/>
+      <c r="S14" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T11" s="11" t="inlineStr">
+      <c r="T14" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
+      <c r="U14" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>E2E-04-002</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Server recomputes totals</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Totals cannot be changed from the browser.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>An item in the cart</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Change a price in the page with DevTools before placing</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>1. Edit the shown total in DevTools
 2. Place the order
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>The order uses the server's price; the edited number has no effect.</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
-      <c r="Q12" s="11" t="inlineStr"/>
-      <c r="R12" s="11" t="inlineStr"/>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr"/>
+      <c r="Q15" s="11" t="inlineStr"/>
+      <c r="R15" s="11" t="inlineStr"/>
+      <c r="S15" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr">
+      <c r="T15" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U12" s="11" t="inlineStr">
+      <c r="U15" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>E2E-04-003</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Confirmation page is private</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Only the browser that placed the order sees the confirmation.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>E2E-04-001 done</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>The confirmation address</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>1. Open the confirmation address in another browser
 2. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>"We can't show this order here".</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
-      <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
-      <c r="S13" s="11" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr"/>
+      <c r="Q16" s="11" t="inlineStr"/>
+      <c r="R16" s="11" t="inlineStr"/>
+      <c r="S16" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T13" s="11" t="inlineStr">
+      <c r="T16" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U13" s="11" t="inlineStr">
+      <c r="U16" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>E2E-04-004</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Fulfilment</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>CMS sees, packs, ships, delivers</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>The order flows through the CMS and messages.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>E2E-04-001 done</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>Tracking 12345</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>1. Owner: Sales → Orders → open the order
 2. Mark as packed
@@ -32776,267 +33048,267 @@
 8. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>Invoice issued at packing; order Completed, Paid, Delivered; messages queued then "Sent (dev log)" for each step.</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr"/>
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
-      <c r="Q14" s="11" t="inlineStr"/>
-      <c r="R14" s="11" t="inlineStr"/>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr"/>
+      <c r="Q17" s="11" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr"/>
+      <c r="S17" s="11" t="inlineStr">
         <is>
           <t>Store owner</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr">
+      <c r="T17" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U14" s="11" t="inlineStr">
+      <c r="U17" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>E2E-04-005</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>No-login tracking page</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>The tracking link shows progress without personal details.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Shipped order; link from the message</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>/t/&lt;code&gt;</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>1. Open the tracking link
 2. Open a made-up code
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>Journey, courier and AWB, items and masked phone; no address or invoice. A made-up code: "We can't find this order".</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr"/>
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
-      <c r="Q15" s="11" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr"/>
+      <c r="Q18" s="11" t="inlineStr"/>
+      <c r="R18" s="11" t="inlineStr"/>
+      <c r="S18" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T15" s="11" t="inlineStr">
+      <c r="T18" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U15" s="11" t="inlineStr">
+      <c r="U18" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>E2E-04-006</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Sale reaches the platform dashboard</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>The super admin sees the order in figures.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>E2E-04-001 done today</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>1. Super admin: open the dashboard
 2. Open All vendors
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>Orders today counts it; GMV this month includes it once delivered/paid; Home Orbit's Orders in 30 days goes up.</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
-      <c r="Q16" s="11" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr"/>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>Super admin</t>
         </is>
       </c>
-      <c r="T16" s="11" t="inlineStr">
+      <c r="T19" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="11" t="inlineStr">
+      <c r="U19" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>E2E-04-007</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>E2E-04 · Order to cash (COD)</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Stock held and released</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Stock is held at checkout and returned on cancel.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>A variant with stock 2</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>Order 2, then cancel</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>1. Order both pieces
 2. Try to buy one more
@@ -33045,178 +33317,178 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>"Only 0 left"/Out of stock while held; buyable again after cancel.</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr"/>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
-      <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr"/>
+      <c r="P20" s="11" t="inlineStr"/>
+      <c r="Q20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr"/>
+      <c r="S20" s="11" t="inlineStr">
         <is>
           <t>Shopper, Store owner</t>
         </is>
       </c>
-      <c r="T17" s="11" t="inlineStr">
+      <c r="T20" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U17" s="11" t="inlineStr">
+      <c r="U20" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>E2E-05-001</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>E2E-05 · Schemes and coupons to checkout</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Scheme</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Live scheme prices everywhere</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>A live scheme shows the same price on card, product, cart and order.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Store selling</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>Diwali 2026, 10% off, max ₹1,500, whole store, live now</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>1. Owner: create and schedule the scheme
 2. Store: read a card, the product page, the cart, then place a COD order
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>The same offer price on card and product page; the cart shows the scheme line; the order's discount equals the cart's.</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M21" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
-      <c r="Q18" s="11" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+      <c r="Q21" s="11" t="inlineStr"/>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="11" t="inlineStr">
         <is>
           <t>Store owner, Shopper</t>
         </is>
       </c>
-      <c r="T18" s="11" t="inlineStr">
+      <c r="T21" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U18" s="11" t="inlineStr">
+      <c r="U21" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>E2E-05-002</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>E2E-05 · Schemes and coupons to checkout</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Coupon</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Coupon on product page and cart</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>A public coupon shows as an offer and applies once.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Coupons on</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>HOME200, ₹200 off above ₹1,000, public</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>1. Owner: create HOME200
 2. Store: open a product it covers
@@ -33225,277 +33497,9 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>Offers for you lists HOME200 with Copy; the cart applies ₹200 once; a second code replaces the first (one coupon per order).</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
-      <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>Store owner, Shopper</t>
-        </is>
-      </c>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>E2E-05-003</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>E2E-05 · Schemes and coupons to checkout</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Scheme</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Upcoming scheme shown honestly</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>A scheduled scheme shows its real start date.</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>A scheme starting next week with Show before start</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>1. Store: open a covered product
-2. Open /offers
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>Offers for you says "from &lt;real start date&gt;"; /offers lists it as coming up; prices are not changed yet.</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr"/>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
-      <c r="Q20" s="11" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr"/>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>Shopper</t>
-        </is>
-      </c>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U20" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>E2E-06-001</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>E2E-06 · Review lifecycle</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Reviews</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Delivered buyer writes, store approves, store shows</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>The full review cycle.</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>A delivered order for shopper rahul.k@example.com with an account</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>2 stars, title, text, a photo</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>1. Shopper: My account → Write a review on the delivered order
-2. Owner: Marketing → Reviews → Approve with reply
-3. Store: open the product and a category
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Product page shows the review with "Verified purchase" and the reply; cards show stars; the home page Reviews block shows it if 4+ stars only.</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>Shopper, Store owner</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>E2E-06-002</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>E2E-06 · Review lifecycle</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Reviews</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Non-buyers cannot review</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Only delivered items can be reviewed.</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>A shopper with no delivered order</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>1. Look for Write a review in My account
-2. Open a review link for another order
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>No Write a review; foreign or expired links are refused.</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr"/>
@@ -33511,7 +33515,7 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr"/>
@@ -33520,7 +33524,7 @@
       <c r="R22" s="11" t="inlineStr"/>
       <c r="S22" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Store owner, Shopper</t>
         </is>
       </c>
       <c r="T22" s="11" t="inlineStr">
@@ -33530,52 +33534,320 @@
       </c>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
+          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>E2E-05-003</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>E2E-05 · Schemes and coupons to checkout</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Scheme</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Upcoming scheme shown honestly</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>A scheduled scheme shows its real start date.</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>A scheme starting next week with Show before start</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>1. Store: open a covered product
+2. Open /offers
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Offers for you says "from &lt;real start date&gt;"; /offers lists it as coming up; prices are not changed yet.</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr"/>
+      <c r="Q23" s="11" t="inlineStr"/>
+      <c r="R23" s="11" t="inlineStr"/>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>E2E-06-001</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>E2E-06 · Review lifecycle</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Delivered buyer writes, store approves, store shows</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>The full review cycle.</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>A delivered order for shopper rahul.k@example.com with an account</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>2 stars, title, text, a photo</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>1. Shopper: My account → Write a review on the delivered order
+2. Owner: Marketing → Reviews → Approve with reply
+3. Store: open the product and a category
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Product page shows the review with "Verified purchase" and the reply; cards show stars; the home page Reviews block shows it if 4+ stars only.</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr"/>
+      <c r="Q24" s="11" t="inlineStr"/>
+      <c r="R24" s="11" t="inlineStr"/>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Store owner</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>E2E-06-002</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>E2E-06 · Review lifecycle</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Non-buyers cannot review</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Only delivered items can be reviewed.</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>A shopper with no delivered order</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>1. Look for Write a review in My account
+2. Open a review link for another order
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>No Write a review; foreign or expired links are refused.</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr"/>
+      <c r="Q25" s="11" t="inlineStr"/>
+      <c r="R25" s="11" t="inlineStr"/>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>E2E-07-001</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>E2E-07 · Store status across portals</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Go live, suspend, resume</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Store status reaches shoppers and search engines.</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Home Orbit draft</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Reasons for suspend</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>1. Super admin: Go live
 2. Store: reload; open /robots.txt and /sitemap.xml
@@ -33585,89 +33857,89 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>Live: no preview bar, robots allows, sitemap lists home, 13 categories and 110 products. Suspended: "Store unavailable", robots Disallow, sitemap gone. Resumed: back at once. Recent changes lists all with reasons.</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr"/>
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr"/>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr">
+      <c r="O26" s="11" t="inlineStr"/>
+      <c r="P26" s="11" t="inlineStr"/>
+      <c r="Q26" s="11" t="inlineStr"/>
+      <c r="R26" s="11" t="inlineStr"/>
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>Super admin, Shopper</t>
         </is>
       </c>
-      <c r="T23" s="11" t="inlineStr">
+      <c r="T26" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U23" s="11" t="inlineStr">
+      <c r="U26" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-07-store-status.md</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>E2E-07-002</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>E2E-07 · Store status across portals</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Suspended store refuses orders</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>A suspended store cannot take orders even from an open checkout.</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Checkout open in a tab</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>1. Open checkout with an item
 2. Super admin suspends the store
@@ -33675,89 +33947,89 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>The order is refused; no order is created.</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
-      <c r="Q24" s="11" t="inlineStr"/>
-      <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
+      <c r="Q27" s="11" t="inlineStr"/>
+      <c r="R27" s="11" t="inlineStr"/>
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>Shopper, Super admin</t>
         </is>
       </c>
-      <c r="T24" s="11" t="inlineStr">
+      <c r="T27" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U24" s="11" t="inlineStr">
+      <c r="U27" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-07-store-status.md</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>E2E-08-001</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>E2E-08 · Platform support session audit</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Audited manage session</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Changes made by the platform inside a store are visible to the store and the platform.</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Super admin and owner</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>Reason "Vendor asked us to set up the Diwali page"</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>1. Super admin: Manage store with the reason
 2. Edit About us; Save Draft
@@ -33767,276 +34039,9 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>Owner sees "by Platform Admin (platform team)"; Recent changes lists the session, reason and edit.</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr"/>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr"/>
-      <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>Super admin, Store owner</t>
-        </is>
-      </c>
-      <c r="T25" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U25" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>E2E-08-002</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>E2E-08 · Platform support session audit</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Support view cannot change data</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>View as support never saves.</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>View as support session</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>1. Try to save a product and a setting
-2. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>Nothing saves; no Save buttons or the save is refused.</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr"/>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>Security/Permissions</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr"/>
-      <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>Super admin</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>E2E-09-001</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>E2E-09 · Connector allowance to checkout</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Connectors</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Razorpay blocked by the platform</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>A disallowed provider is unusable for the store.</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Razorpay keys saved by the owner</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>1. Super admin: Connectors → Razorpay Allowed off
-2. Owner: open Payments
-3. Shopper: open checkout
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>Payments says Razorpay is not allowed; checkout offers no Pay online (COD only if on); switching it back restores.</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="inlineStr"/>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="inlineStr"/>
-      <c r="P27" s="11" t="inlineStr"/>
-      <c r="Q27" s="11" t="inlineStr"/>
-      <c r="R27" s="11" t="inlineStr"/>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>Super admin, Store owner, Shopper</t>
-        </is>
-      </c>
-      <c r="T27" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>E2E-09-002</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>E2E-09 · Connector allowance to checkout</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Connectors</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>COD rules at checkout</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>COD rules from Payments apply at checkout and show to the platform.</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>COD ₹499–₹25,000, fee ₹49</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>Carts ₹300 and ₹600</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>1. Shopper: checkout with ₹300 then ₹600
-2. Super admin: Connectors tab
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>₹300 has no COD; ₹600 offers COD with ₹49; the platform shows the vendor's rules.</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -34052,7 +34057,7 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr"/>
@@ -34061,7 +34066,7 @@
       <c r="R28" s="11" t="inlineStr"/>
       <c r="S28" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Super admin</t>
+          <t>Super admin, Store owner</t>
         </is>
       </c>
       <c r="T28" s="11" t="inlineStr">
@@ -34071,52 +34076,319 @@
       </c>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
+          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t>E2E-08-002</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>E2E-08 · Platform support session audit</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Support view cannot change data</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>View as support never saves.</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>View as support session</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>1. Try to save a product and a setting
+2. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Nothing saves; no Save buttons or the save is refused.</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr"/>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
+      <c r="Q29" s="11" t="inlineStr"/>
+      <c r="R29" s="11" t="inlineStr"/>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>Super admin</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>E2E-09-001</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>E2E-09 · Connector allowance to checkout</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Connectors</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Razorpay blocked by the platform</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>A disallowed provider is unusable for the store.</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Razorpay keys saved by the owner</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>1. Super admin: Connectors → Razorpay Allowed off
+2. Owner: open Payments
+3. Shopper: open checkout
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Payments says Razorpay is not allowed; checkout offers no Pay online (COD only if on); switching it back restores.</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="inlineStr"/>
+      <c r="P30" s="11" t="inlineStr"/>
+      <c r="Q30" s="11" t="inlineStr"/>
+      <c r="R30" s="11" t="inlineStr"/>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>Super admin, Store owner, Shopper</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>E2E-09-002</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>E2E-09 · Connector allowance to checkout</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Connectors</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>COD rules at checkout</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>COD rules from Payments apply at checkout and show to the platform.</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>COD ₹499–₹25,000, fee ₹49</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Carts ₹300 and ₹600</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>1. Shopper: checkout with ₹300 then ₹600
+2. Super admin: Connectors tab
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>₹300 has no COD; ₹600 offers COD with ₹49; the platform shows the vendor's rules.</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="11" t="inlineStr"/>
+      <c r="R31" s="11" t="inlineStr"/>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Super admin</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>E2E-10-001</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>E2E-10 · Staff roles and two-step reset</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Order manager limits</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>An order manager handles orders but not keys, staff or catalogue writes.</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Owner invites orders@homeorbit.example as Order manager</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>1. Accept the invite in another browser
 2. Pack an order
@@ -34125,276 +34397,9 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>Orders work; payments and staff refused; product editing refused or read-only.</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr"/>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Security/Permissions</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="inlineStr"/>
-      <c r="P29" s="11" t="inlineStr"/>
-      <c r="Q29" s="11" t="inlineStr"/>
-      <c r="R29" s="11" t="inlineStr"/>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>Store owner, Order manager</t>
-        </is>
-      </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U29" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>E2E-10-002</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>E2E-10 · Staff roles and two-step reset</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Two-step</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Platform resets a staff member's two-step</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>A vendor staff member who lost their phone is reset by the super admin.</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>Staff member with two-step On</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>1. Super admin: Home Orbit → Staff → Reset two-step
-2. Staff member signs in
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>They sign in with the password only and can set two-step again; the reset is in the audit log.</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr"/>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>Security/Permissions</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="inlineStr"/>
-      <c r="P30" s="11" t="inlineStr"/>
-      <c r="Q30" s="11" t="inlineStr"/>
-      <c r="R30" s="11" t="inlineStr"/>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>Super admin, Store staff</t>
-        </is>
-      </c>
-      <c r="T30" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U30" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>E2E-11-001</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>E2E-11 · Tenant isolation</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Isolation</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Another store's records are invisible</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Demo Sanitary's owner cannot see Home Orbit data.</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Both owners signed in</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>A Home Orbit product address</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>1. Demo Sanitary owner: open Products, Categories, Media, Enquiries, Orders
-2. Paste a Home Orbit product's admin address
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>All lists show only Demo Sanitary's records; the pasted address says it could not be found or no access.</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr"/>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N31" s="11" t="inlineStr">
-        <is>
-          <t>Security/Permissions</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr"/>
-      <c r="P31" s="11" t="inlineStr"/>
-      <c r="Q31" s="11" t="inlineStr"/>
-      <c r="R31" s="11" t="inlineStr"/>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>Store owners</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U31" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>E2E-11-002</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>E2E-11 · Tenant isolation</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Isolation</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Shopper logins are per store</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>A shopper account on one store does not sign in on another.</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Shopper account on Home Orbit</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Same email on demo-sanitary.localhost</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>1. Sign in on Home Orbit
-2. Open http://demo-sanitary.localhost:3000/account
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>Not signed in on Demo Sanitary; the same email there is a separate account.</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -34405,7 +34410,7 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
@@ -34419,24 +34424,24 @@
       <c r="R32" s="11" t="inlineStr"/>
       <c r="S32" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Store owner, Order manager</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
+          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>E2E-11-003</t>
+          <t>E2E-10-002</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -34446,43 +34451,44 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>E2E-11 · Tenant isolation</t>
+          <t>E2E-10 · Staff roles and two-step reset</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Two-step</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>API reads are scoped</t>
+          <t>Platform resets a staff member's two-step</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>The REST API never returns another store's records.</t>
+          <t>A vendor staff member who lost their phone is reset by the super admin.</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Signed in as Demo Sanitary owner</t>
+          <t>Staff member with two-step On</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>/api/products?limit=5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>1. Open /api/products?limit=5 in the browser
-2. Verify the expected result.</t>
+          <t>1. Super admin: Home Orbit → Staff → Reset two-step
+2. Staff member signs in
+3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>Only Demo Sanitary's products (or none); never Home Orbit's.</t>
+          <t>They sign in with the password only and can set two-step again; the reset is in the audit log.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr"/>
@@ -34493,7 +34499,7 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -34507,7 +34513,7 @@
       <c r="R33" s="11" t="inlineStr"/>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>Store owner</t>
+          <t>Super admin, Store staff</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr">
@@ -34517,14 +34523,14 @@
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
+          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>E2E-12-001</t>
+          <t>E2E-11-001</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -34534,45 +34540,44 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>E2E-12 · Enquiry from store to inbox</t>
+          <t>E2E-11 · Tenant isolation</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Enquiry</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Quote to inbox to closed</t>
+          <t>Another store's records are invisible</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>A product quote request reaches the inbox and is worked.</t>
+          <t>Demo Sanitary's owner cannot see Home Orbit data.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Enquiries on</t>
+          <t>Both owners signed in</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Name, 10-digit mobile, city, quantity 50, consent ticked; options picked</t>
+          <t>A Home Orbit product address</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>1. Store: product page → Request a bulk quote with the data
-2. Owner: dashboard figures and bell
-3. Inbox: open it, assign, Contacted, note, Won
-4. Verify the expected result.</t>
+          <t>1. Demo Sanitary owner: open Products, Categories, Media, Enquiries, Orders
+2. Paste a Home Orbit product's admin address
+3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>Store says thanks with ENQ-n; dashboard and bell count it; the inbox shows the options; it moves New → In progress → Closed.</t>
+          <t>All lists show only Demo Sanitary's records; the pasted address says it could not be found or no access.</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -34588,7 +34593,7 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security/Permissions</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr"/>
@@ -34597,7 +34602,7 @@
       <c r="R34" s="11" t="inlineStr"/>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Store owner</t>
+          <t>Store owners</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr">
@@ -34607,145 +34612,412 @@
       </c>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
+          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
+          <t>E2E-11-002</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>E2E-11 · Tenant isolation</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Isolation</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Shopper logins are per store</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>A shopper account on one store does not sign in on another.</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Shopper account on Home Orbit</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Same email on demo-sanitary.localhost</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>1. Sign in on Home Orbit
+2. Open http://demo-sanitary.localhost:3000/account
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Not signed in on Demo Sanitary; the same email there is a separate account.</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr"/>
+      <c r="R35" s="11" t="inlineStr"/>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>E2E-11-003</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>E2E-11 · Tenant isolation</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Isolation</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>API reads are scoped</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>The REST API never returns another store's records.</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Signed in as Demo Sanitary owner</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>/api/products?limit=5</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>1. Open /api/products?limit=5 in the browser
+2. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Only Demo Sanitary's products (or none); never Home Orbit's.</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr"/>
+      <c r="R36" s="11" t="inlineStr"/>
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>Store owner</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>E2E-12-001</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>E2E-12 · Enquiry from store to inbox</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Enquiry</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Quote to inbox to closed</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>A product quote request reaches the inbox and is worked.</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Enquiries on</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Name, 10-digit mobile, city, quantity 50, consent ticked; options picked</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>1. Store: product page → Request a bulk quote with the data
+2. Owner: dashboard figures and bell
+3. Inbox: open it, assign, Contacted, note, Won
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Store says thanks with ENQ-n; dashboard and bell count it; the inbox shows the options; it moves New → In progress → Closed.</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="11" t="inlineStr"/>
+      <c r="R37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Store owner</t>
+        </is>
+      </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>E2E-12-002</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>E2E-12 · Enquiry from store to inbox</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Enquiry</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Validation and spam limit</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>The quote form validates and limits repeats.</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>Empty form; then 6 sends in 10 minutes</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>1. Send the form empty
 2. Send a valid form 6 times quickly
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>Errors under Name and consent and "Add a mobile number or an email…"; the 6th send is refused with the wait message.</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr"/>
-      <c r="L35" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
+      <c r="M38" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N38" s="11" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr"/>
-      <c r="P35" s="11" t="inlineStr"/>
-      <c r="Q35" s="11" t="inlineStr"/>
-      <c r="R35" s="11" t="inlineStr">
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr"/>
+      <c r="R38" s="11" t="inlineStr">
         <is>
           <t>Also: Boundary</t>
         </is>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T35" s="11" t="inlineStr">
+      <c r="T38" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U35" s="11" t="inlineStr">
+      <c r="U38" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>E2E-13-001</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>E2E-13 · Returns and refunds</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Request, approve, receive, refund</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>A return runs from the shopper to a refund and the report.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>A delivered order for a shopper account</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>Reason, note, a photo</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>1. Shopper: order page → Request return
 2. Owner: Orders → Returns → Approve with pickup note
@@ -34754,89 +35026,89 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>Shopper sees each state; the return reads Refunded; a credit note lowers the GST summary row.</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr"/>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="M39" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N36" s="11" t="inlineStr">
+      <c r="N39" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O36" s="11" t="inlineStr"/>
-      <c r="P36" s="11" t="inlineStr"/>
-      <c r="Q36" s="11" t="inlineStr"/>
-      <c r="R36" s="11" t="inlineStr"/>
-      <c r="S36" s="11" t="inlineStr">
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr"/>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>Shopper, Store owner</t>
         </is>
       </c>
-      <c r="T36" s="11" t="inlineStr">
+      <c r="T39" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U36" s="11" t="inlineStr">
+      <c r="U39" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-13-returns.md</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>E2E-14-001</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>E2E-14 · Offer consent, abandoned cart and unsubscribe</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Consent drives reminders; unsubscribe stops offers only</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>Offer consent at checkout and unsubscribe behave as promised.</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>Offer messages and abandoned cart on</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>Tick "Offers and new launches · By email"</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>1. Shopper: checkout, tick offers by email, leave
 2. After the delay: reminder in the terminal; Return to your cart restores it
@@ -34846,279 +35118,9 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>Reminder sent with consent; after unsubscribe no offer message is sent to that email, but order updates still are.</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr"/>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N37" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O37" s="11" t="inlineStr"/>
-      <c r="P37" s="11" t="inlineStr"/>
-      <c r="Q37" s="11" t="inlineStr"/>
-      <c r="R37" s="11" t="inlineStr"/>
-      <c r="S37" s="11" t="inlineStr">
-        <is>
-          <t>Shopper, Store owner</t>
-        </is>
-      </c>
-      <c r="T37" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U37" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-14-abandoned.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>E2E-15-001</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>E2E-15 · Affiliate referral to commission</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Affiliate</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>Referral to approved commission</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>An affiliate link credits the order without exposing the shopper.</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>Approved affiliate</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>/r/&lt;CODE&gt;?to=/products/&lt;slug&gt;</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>1. Open the link in another browser; place a COD order
-2. Affiliate: /affiliate/dashboard
-3. Owner: deliver the order; wait the hold days or run the job
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>Dashboard shows the order "Pending: not delivered yet" without shopper details; after delivery and hold it becomes approved; cancelling reverses it.</t>
-        </is>
-      </c>
-      <c r="K38" s="11" t="inlineStr"/>
-      <c r="L38" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O38" s="11" t="inlineStr"/>
-      <c r="P38" s="11" t="inlineStr"/>
-      <c r="Q38" s="11" t="inlineStr"/>
-      <c r="R38" s="11" t="inlineStr"/>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>Affiliate, Shopper, Store owner</t>
-        </is>
-      </c>
-      <c r="T38" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U38" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-15-affiliate.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>E2E-16-001</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>E2E-16 · Billing to subscriptions</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Billing</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Payment updates subscriptions and MRR</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>Recording a vendor payment changes the platform money views.</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>A trial or past-due vendor</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>₹9,999</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>1. Super admin: note Subscriptions and dashboard figures
-2. Record a payment on the vendor's Billing
-3. Reload Subscriptions and the dashboard
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>The subscription is Active with the new period; Past due and MRR change accordingly.</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr"/>
-      <c r="L39" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M39" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O39" s="11" t="inlineStr"/>
-      <c r="P39" s="11" t="inlineStr"/>
-      <c r="Q39" s="11" t="inlineStr"/>
-      <c r="R39" s="11" t="inlineStr"/>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>Super admin</t>
-        </is>
-      </c>
-      <c r="T39" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U39" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-16-billing.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>E2E-17-001</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>E2E-17 · Shopper account and wishlist across devices</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>Guest orders join the account</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>Logging in with the checkout email shows earlier guest orders.</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>A guest COD order with rahul.k@example.com</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>Code from the terminal</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>1. Open http://home-orbit.localhost:3000/account → Send code to the email
-2. Type the code from the terminal
-3. Read Your orders
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>My account "Hi Rahul" lists the guest order with Track order and Invoice.</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -35143,7 +35145,7 @@
       <c r="R40" s="11" t="inlineStr"/>
       <c r="S40" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Shopper, Store owner</t>
         </is>
       </c>
       <c r="T40" s="11" t="inlineStr">
@@ -35153,14 +35155,14 @@
       </c>
       <c r="U40" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+          <t>docs/qa/regression/e2e/E2E-14-abandoned.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>E2E-17-002</t>
+          <t>E2E-15-001</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -35170,45 +35172,45 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>E2E-17 · Shopper account and wishlist across devices</t>
+          <t>E2E-15 · Affiliate referral to commission</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>Affiliate</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Wishlist follows sign-in</t>
+          <t>Referral to approved commission</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>A guest wishlist merges into the account and shows on another browser.</t>
+          <t>An affiliate link credits the order without exposing the shopper.</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Wishlist on</t>
+          <t>Approved affiliate</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/r/&lt;CODE&gt;?to=/products/&lt;slug&gt;</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>1. As a guest tap the heart on two cards
-2. Log in
-3. Open /wishlist in another browser signed in
+          <t>1. Open the link in another browser; place a COD order
+2. Affiliate: /affiliate/dashboard
+3. Owner: deliver the order; wait the hold days or run the job
 4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>Both products in the wishlist on both browsers; the header heart shows 2.</t>
+          <t>Dashboard shows the order "Pending: not delivered yet" without shopper details; after delivery and hold it becomes approved; cancelling reverses it.</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -35224,7 +35226,7 @@
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr"/>
@@ -35233,7 +35235,7 @@
       <c r="R41" s="11" t="inlineStr"/>
       <c r="S41" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Affiliate, Shopper, Store owner</t>
         </is>
       </c>
       <c r="T41" s="11" t="inlineStr">
@@ -35243,14 +35245,14 @@
       </c>
       <c r="U41" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+          <t>docs/qa/regression/e2e/E2E-15-affiliate.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>E2E-17-003</t>
+          <t>E2E-16-001</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -35260,44 +35262,45 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>E2E-17 · Shopper account and wishlist across devices</t>
+          <t>E2E-16 · Billing to subscriptions</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Log out of all devices</t>
+          <t>Payment updates subscriptions and MRR</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Logging out everywhere ends other sessions.</t>
+          <t>Recording a vendor payment changes the platform money views.</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Signed in on two browsers</t>
+          <t>A trial or past-due vendor</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>₹9,999</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>1. Press Log out of all devices on one
-2. Open a page on the other
-3. Verify the expected result.</t>
+          <t>1. Super admin: note Subscriptions and dashboard figures
+2. Record a payment on the vendor's Billing
+3. Reload Subscriptions and the dashboard
+4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>The other browser is signed out on its next page.</t>
+          <t>The subscription is Active with the new period; Past due and MRR change accordingly.</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -35308,12 +35311,12 @@
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O42" s="11" t="inlineStr"/>
@@ -35322,7 +35325,7 @@
       <c r="R42" s="11" t="inlineStr"/>
       <c r="S42" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Super admin</t>
         </is>
       </c>
       <c r="T42" s="11" t="inlineStr">
@@ -35332,52 +35335,321 @@
       </c>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+          <t>docs/qa/regression/e2e/E2E-16-billing.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
+          <t>E2E-17-001</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17 · Shopper account and wishlist across devices</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Guest orders join the account</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Logging in with the checkout email shows earlier guest orders.</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>A guest COD order with rahul.k@example.com</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Code from the terminal</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>1. Open http://home-orbit.localhost:3000/account → Send code to the email
+2. Type the code from the terminal
+3. Read Your orders
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>My account "Hi Rahul" lists the guest order with Track order and Invoice.</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="11" t="inlineStr"/>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T43" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17-002</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17 · Shopper account and wishlist across devices</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Wishlist</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Wishlist follows sign-in</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>A guest wishlist merges into the account and shows on another browser.</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Wishlist on</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>1. As a guest tap the heart on two cards
+2. Log in
+3. Open /wishlist in another browser signed in
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Both products in the wishlist on both browsers; the header heart shows 2.</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>Data persistence</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr"/>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T44" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17-003</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17 · Shopper account and wishlist across devices</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Log out of all devices</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>Logging out everywhere ends other sessions.</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Signed in on two browsers</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>1. Press Log out of all devices on one
+2. Open a page on the other
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>The other browser is signed out on its next page.</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="11" t="inlineStr"/>
+      <c r="R45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T45" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>E2E-18-001</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>Desktop header icons and menu</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>The desktop header has the menu, search and icons and never overflows.</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>Store selling; wishlist on</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>Widths 1280 and 1024</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>1. Open http://home-orbit.localhost:3000 at 1280 px
 2. Read the header
@@ -35385,105 +35657,105 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>Menu items on one line, search box, account, wishlist with count and cart with count; at 1024 the search becomes an icon and nothing overlaps.</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>At 1280 px: menu on one line, search box, account, wishlist and cart icons; at 1024 px the search became an icon and the menu no longer overlapped.</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="L46" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
+      <c r="M46" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="N46" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O43" s="11" t="inlineStr">
+      <c r="O46" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P43" s="11" t="inlineStr">
+      <c r="P46" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q43" s="11" t="inlineStr"/>
-      <c r="R43" s="11" t="inlineStr">
+      <c r="Q46" s="11" t="inlineStr"/>
+      <c r="R46" s="11" t="inlineStr">
         <is>
           <t>Found and fixed in the same session (search box covered "About us" at 1024 px).</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T43" s="11" t="inlineStr">
+      <c r="T46" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U43" s="11" t="inlineStr">
+      <c r="U46" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>E2E-18-002</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Bottom navigation</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>The phone bottom bar shows the right tabs and hides on pages with their own bar.</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Phone size (375 px)</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>1. Read the bottom bar on the home page
 2. Tap Shop
@@ -35491,205 +35763,205 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>Home, Shop, Dealers, Account, Cart; Shop opens /c with all categories; on product, cart and checkout the page's sticky button replaces the bar.</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>Phone: bottom bar Home, Shop, Dealers, Account, Cart; Shop opened /c; on a product page the sticky "₹1,049 Add to cart" bar replaced it.</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="L47" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="M47" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O44" s="11" t="inlineStr">
+      <c r="O47" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P44" s="11" t="inlineStr">
+      <c r="P47" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q44" s="11" t="inlineStr"/>
-      <c r="R44" s="11" t="inlineStr"/>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="Q47" s="11" t="inlineStr"/>
+      <c r="R47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T44" s="11" t="inlineStr">
+      <c r="T47" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U44" s="11" t="inlineStr">
+      <c r="U47" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>E2E-18-003</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Footer columns and legal line</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>The footer matches the wireframe and the store's features.</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>Store selling; contact and grievance officer saved (VC-03)</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>1. Scroll to the footer
 2. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>Logo, contact, Get our offers first; Shop with Offers; Help with Track order, published policies, Contact us; Company with Find a dealer and Downloads; legal name, GSTIN, grievance officer and ways to pay.</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>Footer: Get our offers first, Shop (with Offers), Help (Track order, Contact us), Company (About us, Contact us, Find a dealer, Downloads), legal line with name and GSTIN, COD chip.</t>
         </is>
       </c>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="L48" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N48" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O45" s="11" t="inlineStr">
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="P48" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q45" s="11" t="inlineStr"/>
-      <c r="R45" s="11" t="inlineStr">
+      <c r="Q48" s="11" t="inlineStr"/>
+      <c r="R48" s="11" t="inlineStr">
         <is>
           <t>QA data has placeholder business details and no grievance officer or published policies, so those lines were not shown.</t>
         </is>
       </c>
-      <c r="S45" s="11" t="inlineStr">
+      <c r="S48" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T45" s="11" t="inlineStr">
+      <c r="T48" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U45" s="11" t="inlineStr">
+      <c r="U48" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>E2E-18-004</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Instant search with typos and recent searches</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>Suggestions rank model numbers first and forgive typos.</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Store with Home Orbit's catalogue</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>"610"; "hogdh610"; "glas handel"</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>1. Type each in the header search
 2. Use arrow keys and Enter
@@ -35697,105 +35969,105 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>HOGDH-610 first for the first two; glass door handles for the typo; Enter opens the choice; Recent searches list earlier terms.</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>"610" and "hogdh610" → HOGDH-610 first; "key" → key hangers and the Key hangers category; "glas handel" → glass door handles (after the swapped-letter fix).</t>
         </is>
       </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="L49" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M46" s="11" t="inlineStr">
+      <c r="M49" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N46" s="11" t="inlineStr">
+      <c r="N49" s="11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O46" s="11" t="inlineStr">
+      <c r="O49" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P46" s="11" t="inlineStr">
+      <c r="P49" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q46" s="11" t="inlineStr"/>
-      <c r="R46" s="11" t="inlineStr">
+      <c r="Q49" s="11" t="inlineStr"/>
+      <c r="R49" s="11" t="inlineStr">
         <is>
           <t>Arrow keys and Recent searches were not exercised.</t>
         </is>
       </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="S49" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T46" s="11" t="inlineStr">
+      <c r="T49" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U46" s="11" t="inlineStr">
+      <c r="U49" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>E2E-18-005</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>Listing</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Filter sheet on phones</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>The phone filter sheet works and reports the count.</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>Phone size; store selling</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>Price 500–1000</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>1. Open a category
 2. Tap Filter
@@ -35804,101 +36076,101 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>A sheet over a dimmed page with Close and Clear; the count matches the list; Filter (1) after closing.</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>Filter sheet opened over the page with Close, Price, Clear and "Show 50 products"; price 500–1000 gave 21 products, Price low to high cheapest first.</t>
         </is>
       </c>
-      <c r="L47" s="11" t="inlineStr">
+      <c r="L50" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M47" s="11" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="N50" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="O50" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
+      <c r="P50" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q47" s="11" t="inlineStr"/>
-      <c r="R47" s="11" t="inlineStr"/>
-      <c r="S47" s="11" t="inlineStr">
+      <c r="Q50" s="11" t="inlineStr"/>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T47" s="11" t="inlineStr">
+      <c r="T50" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U47" s="11" t="inlineStr">
+      <c r="U50" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>E2E-18-006</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Move to wishlist and Complete the look</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>Cart extras work.</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Two items in the cart; wishlist on</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>1. Press Move to wishlist on one line
 2. Read Complete the look
@@ -35906,62 +36178,62 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>The line leaves the cart and the heart count goes up; suggestions come from the same categories and Add to cart adds one.</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>Move to wishlist removed the door stopper from the cart and the heart read "1 saved"; Complete the look listed 4 products with Add to cart.</t>
         </is>
       </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="L51" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M48" s="11" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N48" s="11" t="inlineStr">
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr">
+      <c r="O51" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P48" s="11" t="inlineStr">
+      <c r="P51" s="11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Q48" s="11" t="inlineStr"/>
-      <c r="R48" s="11" t="inlineStr"/>
-      <c r="S48" s="11" t="inlineStr">
+      <c r="Q51" s="11" t="inlineStr"/>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T48" s="11" t="inlineStr">
+      <c r="T51" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U48" s="11" t="inlineStr">
+      <c r="U51" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U48"/>
-  <conditionalFormatting sqref="L2:L248">
+  <autoFilter ref="A1:U51"/>
+  <conditionalFormatting sqref="L2:L251">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -35978,25 +36250,25 @@
       <formula>"Not Applicable"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M248">
+  <conditionalFormatting sqref="M2:M251">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="L2:L248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="L2:L251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="M2:M251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="N2:N251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Functional,Regression,Negative,Validation,Boundary,Integration,UI/UX,Security/Permissions,Data persistence,Accessibility"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="B2:B251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Super Admin,Vendor CMS,End-to-End"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="T2:T251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/TenantEcom-test-cases.xlsx
+++ b/docs/qa/TenantEcom-test-cases.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vendor CMS'!$A$1:$U$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Super Admin'!$A$1:$U$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defect Log'!$A$1:$M$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defect Log'!$A$1:$M$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-11 from docs/qa/tools. Figures recalculate as Status cells change.</t>
+          <t>Generated 2026-10-13 from docs/qa/tools. Figures recalculate as Status cells change.</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32313,7 +32313,7 @@
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>Category card Add to cart: "Added ✓" and the cart count went from 2 to 3 without leaving the page.</t>
+          <t>Door hardware sorted Price: low to high (₹249, ₹249, ₹249, ₹349…); Add to cart on HODS-861 made the cart 1 item.</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -32338,13 +32338,13 @@
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>Run on existing Home Orbit products, not a new QA product.</t>
+          <t>First try failed after an order in the same browser (DEF-003); passed after the fix.</t>
         </is>
       </c>
       <c r="S9" s="11" t="inlineStr">
@@ -32597,10 +32597,14 @@
           <t>The picker shows sizes and finish swatches, the price changes with the choice, code HOPH-504-12-INCH-ROSE-GOLD shows; "Added to your cart. View cart" and the count goes up; Esc closes it.</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Phone: Quick add on HOPH-504 opened the picker sheet (sizes and finishes, ₹2,049); Add to cart bumped the cart to 1; Escape closed it.</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -32613,8 +32617,16 @@
           <t>Integration</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q12" s="11" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="11" t="inlineStr">
@@ -32688,10 +32700,14 @@
           <t>Three headed columns, the aldrop picture and Shop all door hardware; Laser-cut aldrops opens Aldrops filtered to the laser-cut range (4 products); after the edit the column reads "Handles".</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>Focus on Door hardware opened the dropdown: Aldrops and latches with All aldrops, Laser-cut aldrops, BMC-cut aldrops…</t>
+        </is>
+      </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -32704,10 +32720,22 @@
           <t>Integration</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr">
+        <is>
+          <t>Menus edit step (owner) not repeated.</t>
+        </is>
+      </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
           <t>Shopper, Store owner</t>
@@ -32782,10 +32810,14 @@
           <t>"Thank you, Rahul. Your order is placed." with the order number (HOM-…), amount to pay in cash, delivery date and items; the cart is empty again.</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>"Thank you, Rahul. Your order is placed." Order HOM-10024 · ₹1,947.00 to pay in cash on delivery, arrives Thu 15 Oct, both items listed; cart empty; email and WhatsApp printed in the dev log.</t>
+        </is>
+      </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -32798,8 +32830,16 @@
           <t>Integration</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q14" s="11" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="11" t="inlineStr">
@@ -32871,10 +32911,14 @@
           <t>The order uses the server's price; the edited number has no effect.</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>Changed every shown total to ₹1.00 before Place order; the order and messages say ₹1,947 (₹849 + ₹1,049 + ₹49 COD fee).</t>
+        </is>
+      </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -32887,8 +32931,16 @@
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q15" s="11" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="11" t="inlineStr">
@@ -32959,10 +33011,14 @@
           <t>"We can't show this order here".</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>The confirmation address fetched without the shopper's cookies: "We can't show this order here".</t>
+        </is>
+      </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -32975,8 +33031,16 @@
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q16" s="11" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="11" t="inlineStr">
@@ -33142,10 +33206,14 @@
           <t>Journey, courier and AWB, items and masked phone; no address or invoice. A made-up code: "We can't find this order".</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>/t/&lt;code&gt; without cookies: HOM-10024 Confirmed · arriving by Thu 15 Oct with the journey; no address.</t>
+        </is>
+      </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -33158,10 +33226,22 @@
           <t>Security/Permissions</t>
         </is>
       </c>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="Q18" s="11" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>Order not shipped yet, so courier and AWB were not shown.</t>
+        </is>
+      </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
@@ -33361,134 +33441,240 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>E2E-04-008</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>E2E-04 · Order to cash (COD)</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Shop again after an order</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>The browser that placed an order can fill a new cart straight away.</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>E2E-04-001 done in this browser</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Any product</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>1. After the confirmation, open a category
+2. Press Add to cart on a card
+3. Open the cart
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>The cart count goes from 0 to 1 and the cart shows only the new item; the order stays as placed.</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>After HOM-10024, Add to cart on a listing card made the cart 1 item.</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr"/>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>Failed before the fix (DEF-003).</t>
+        </is>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-04-order-to-cash.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>E2E-05-001</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>E2E-05 · Schemes and coupons to checkout</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Scheme</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Live scheme prices everywhere</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>A live scheme shows the same price on card, product, cart and order.</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Store selling</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>Diwali 2026, 10% off, max ₹1,500, whole store, live now</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>1. Owner: create and schedule the scheme
 2. Store: read a card, the product page, the cart, then place a COD order
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>The same offer price on card and product page; the cart shows the scheme line; the order's discount equals the cart's.</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr"/>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr"/>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="11" t="inlineStr">
         <is>
           <t>Store owner, Shopper</t>
         </is>
       </c>
-      <c r="T21" s="11" t="inlineStr">
+      <c r="T22" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U21" s="11" t="inlineStr">
+      <c r="U22" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>E2E-05-002</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>E2E-05 · Schemes and coupons to checkout</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Coupon</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Coupon on product page and cart</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>A public coupon shows as an offer and applies once.</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Coupons on</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>HOME200, ₹200 off above ₹1,000, public</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>1. Owner: create HOME200
 2. Store: open a product it covers
@@ -33497,98 +33683,9 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>Offers for you lists HOME200 with Copy; the cart applies ₹200 once; a second code replaces the first (one coupon per order).</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr"/>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>Store owner, Shopper</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>E2E-05-003</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>E2E-05 · Schemes and coupons to checkout</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Scheme</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Upcoming scheme shown honestly</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>A scheduled scheme shows its real start date.</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>A scheme starting next week with Show before start</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>1. Store: open a covered product
-2. Open /offers
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Offers for you says "from &lt;real start date&gt;"; /offers lists it as coming up; prices are not changed yet.</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr"/>
@@ -33599,7 +33696,7 @@
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -33613,7 +33710,7 @@
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Store owner, Shopper</t>
         </is>
       </c>
       <c r="T23" s="11" t="inlineStr">
@@ -33630,7 +33727,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>E2E-06-001</t>
+          <t>E2E-05-003</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -33640,45 +33737,44 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>E2E-06 · Review lifecycle</t>
+          <t>E2E-05 · Schemes and coupons to checkout</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Scheme</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Delivered buyer writes, store approves, store shows</t>
+          <t>Upcoming scheme shown honestly</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>The full review cycle.</t>
+          <t>A scheduled scheme shows its real start date.</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>A delivered order for shopper rahul.k@example.com with an account</t>
+          <t>A scheme starting next week with Show before start</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>2 stars, title, text, a photo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>1. Shopper: My account → Write a review on the delivered order
-2. Owner: Marketing → Reviews → Approve with reply
-3. Store: open the product and a category
-4. Verify the expected result.</t>
+          <t>1. Store: open a covered product
+2. Open /offers
+3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Product page shows the review with "Verified purchase" and the reply; cards show stars; the home page Reviews block shows it if 4+ stars only.</t>
+          <t>Offers for you says "from &lt;real start date&gt;"; /offers lists it as coming up; prices are not changed yet.</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr"/>
@@ -33689,7 +33785,7 @@
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -33703,24 +33799,24 @@
       <c r="R24" s="11" t="inlineStr"/>
       <c r="S24" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Store owner</t>
+          <t>Shopper</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
+          <t>docs/qa/regression/e2e/E2E-05-offers.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>E2E-06-002</t>
+          <t>E2E-06-001</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -33740,34 +33836,35 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Non-buyers cannot review</t>
+          <t>Delivered buyer writes, store approves, store shows</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Only delivered items can be reviewed.</t>
+          <t>The full review cycle.</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>A shopper with no delivered order</t>
+          <t>A delivered order for shopper rahul.k@example.com with an account</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 stars, title, text, a photo</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>1. Look for Write a review in My account
-2. Open a review link for another order
-3. Verify the expected result.</t>
+          <t>1. Shopper: My account → Write a review on the delivered order
+2. Owner: Marketing → Reviews → Approve with reply
+3. Store: open the product and a category
+4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>No Write a review; foreign or expired links are refused.</t>
+          <t>Product page shows the review with "Verified purchase" and the reply; cards show stars; the home page Reviews block shows it if 4+ stars only.</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr"/>
@@ -33778,12 +33875,12 @@
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr"/>
@@ -33792,12 +33889,12 @@
       <c r="R25" s="11" t="inlineStr"/>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Shopper, Store owner</t>
         </is>
       </c>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U25" s="11" t="inlineStr">
@@ -33809,45 +33906,134 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>E2E-06-002</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>E2E-06 · Review lifecycle</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Non-buyers cannot review</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Only delivered items can be reviewed.</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>A shopper with no delivered order</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>1. Look for Write a review in My account
+2. Open a review link for another order
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>No Write a review; foreign or expired links are refused.</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr"/>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr"/>
+      <c r="P26" s="11" t="inlineStr"/>
+      <c r="Q26" s="11" t="inlineStr"/>
+      <c r="R26" s="11" t="inlineStr"/>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-06-reviews.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>E2E-07-001</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>E2E-07 · Store status across portals</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Go live, suspend, resume</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Store status reaches shoppers and search engines.</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Home Orbit draft</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>Reasons for suspend</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>1. Super admin: Go live
 2. Store: reload; open /robots.txt and /sitemap.xml
@@ -33857,99 +34043,9 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>Live: no preview bar, robots allows, sitemap lists home, 13 categories and 110 products. Suspended: "Store unavailable", robots Disallow, sitemap gone. Resumed: back at once. Recent changes lists all with reasons.</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr"/>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr"/>
-      <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>Super admin, Shopper</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-07-store-status.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>E2E-07-002</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>E2E-07 · Store status across portals</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Suspended store refuses orders</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>A suspended store cannot take orders even from an open checkout.</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Checkout open in a tab</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>1. Open checkout with an item
-2. Super admin suspends the store
-3. Place the order
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>The order is refused; no order is created.</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -33960,12 +34056,12 @@
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr"/>
@@ -33974,12 +34070,12 @@
       <c r="R27" s="11" t="inlineStr"/>
       <c r="S27" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Super admin</t>
+          <t>Super admin, Shopper</t>
         </is>
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -33991,45 +34087,135 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>E2E-07-002</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>E2E-07 · Store status across portals</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Suspended store refuses orders</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>A suspended store cannot take orders even from an open checkout.</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Checkout open in a tab</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>1. Open checkout with an item
+2. Super admin suspends the store
+3. Place the order
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>The order is refused; no order is created.</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr"/>
+      <c r="P28" s="11" t="inlineStr"/>
+      <c r="Q28" s="11" t="inlineStr"/>
+      <c r="R28" s="11" t="inlineStr"/>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Super admin</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-07-store-status.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>E2E-08-001</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>E2E-08 · Platform support session audit</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Audited manage session</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Changes made by the platform inside a store are visible to the store and the platform.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Super admin and owner</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>Reason "Vendor asked us to set up the Diwali page"</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>1. Super admin: Manage store with the reason
 2. Edit About us; Save Draft
@@ -34039,97 +34225,9 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>Owner sees "by Platform Admin (platform team)"; Recent changes lists the session, reason and edit.</t>
-        </is>
-      </c>
-      <c r="K28" s="11" t="inlineStr"/>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="inlineStr"/>
-      <c r="P28" s="11" t="inlineStr"/>
-      <c r="Q28" s="11" t="inlineStr"/>
-      <c r="R28" s="11" t="inlineStr"/>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>Super admin, Store owner</t>
-        </is>
-      </c>
-      <c r="T28" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U28" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>E2E-08-002</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>E2E-08 · Platform support session audit</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Support view cannot change data</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>View as support never saves.</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>View as support session</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>1. Try to save a product and a setting
-2. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>Nothing saves; no Save buttons or the save is refused.</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -34145,7 +34243,7 @@
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr"/>
@@ -34154,7 +34252,7 @@
       <c r="R29" s="11" t="inlineStr"/>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>Super admin</t>
+          <t>Super admin, Store owner</t>
         </is>
       </c>
       <c r="T29" s="11" t="inlineStr">
@@ -34171,7 +34269,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>E2E-09-001</t>
+          <t>E2E-08-002</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -34181,27 +34279,27 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>E2E-09 · Connector allowance to checkout</t>
+          <t>E2E-08 · Platform support session audit</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Connectors</t>
+          <t>Session</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Razorpay blocked by the platform</t>
+          <t>Support view cannot change data</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>A disallowed provider is unusable for the store.</t>
+          <t>View as support never saves.</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Razorpay keys saved by the owner</t>
+          <t>View as support session</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -34211,15 +34309,13 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>1. Super admin: Connectors → Razorpay Allowed off
-2. Owner: open Payments
-3. Shopper: open checkout
-4. Verify the expected result.</t>
+          <t>1. Try to save a product and a setting
+2. Verify the expected result.</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>Payments says Razorpay is not allowed; checkout offers no Pay online (COD only if on); switching it back restores.</t>
+          <t>Nothing saves; no Save buttons or the save is refused.</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -34235,7 +34331,7 @@
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security/Permissions</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr"/>
@@ -34244,7 +34340,7 @@
       <c r="R30" s="11" t="inlineStr"/>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>Super admin, Store owner, Shopper</t>
+          <t>Super admin</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr">
@@ -34254,14 +34350,14 @@
       </c>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
+          <t>docs/qa/regression/e2e/E2E-08-support-session.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>E2E-09-002</t>
+          <t>E2E-09-001</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -34281,34 +34377,35 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>COD rules at checkout</t>
+          <t>Razorpay blocked by the platform</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>COD rules from Payments apply at checkout and show to the platform.</t>
+          <t>A disallowed provider is unusable for the store.</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>COD ₹499–₹25,000, fee ₹49</t>
+          <t>Razorpay keys saved by the owner</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Carts ₹300 and ₹600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>1. Shopper: checkout with ₹300 then ₹600
-2. Super admin: Connectors tab
-3. Verify the expected result.</t>
+          <t>1. Super admin: Connectors → Razorpay Allowed off
+2. Owner: open Payments
+3. Shopper: open checkout
+4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>₹300 has no COD; ₹600 offers COD with ₹49; the platform shows the vendor's rules.</t>
+          <t>Payments says Razorpay is not allowed; checkout offers no Pay online (COD only if on); switching it back restores.</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -34324,7 +34421,7 @@
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr"/>
@@ -34333,7 +34430,7 @@
       <c r="R31" s="11" t="inlineStr"/>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Super admin</t>
+          <t>Super admin, Store owner, Shopper</t>
         </is>
       </c>
       <c r="T31" s="11" t="inlineStr">
@@ -34350,45 +34447,134 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t>E2E-09-002</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>E2E-09 · Connector allowance to checkout</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Connectors</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>COD rules at checkout</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>COD rules from Payments apply at checkout and show to the platform.</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>COD ₹499–₹25,000, fee ₹49</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Carts ₹300 and ₹600</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>1. Shopper: checkout with ₹300 then ₹600
+2. Super admin: Connectors tab
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>₹300 has no COD; ₹600 offers COD with ₹49; the platform shows the vendor's rules.</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr"/>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr"/>
+      <c r="P32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr"/>
+      <c r="R32" s="11" t="inlineStr"/>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Super admin</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-09-connectors.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>E2E-10-001</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>E2E-10 · Staff roles and two-step reset</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Order manager limits</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>An order manager handles orders but not keys, staff or catalogue writes.</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Owner invites orders@homeorbit.example as Order manager</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>1. Accept the invite in another browser
 2. Pack an order
@@ -34397,98 +34583,9 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>Orders work; payments and staff refused; product editing refused or read-only.</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr"/>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N32" s="11" t="inlineStr">
-        <is>
-          <t>Security/Permissions</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr"/>
-      <c r="P32" s="11" t="inlineStr"/>
-      <c r="Q32" s="11" t="inlineStr"/>
-      <c r="R32" s="11" t="inlineStr"/>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>Store owner, Order manager</t>
-        </is>
-      </c>
-      <c r="T32" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U32" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>E2E-10-002</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>E2E-10 · Staff roles and two-step reset</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Two-step</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Platform resets a staff member's two-step</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>A vendor staff member who lost their phone is reset by the super admin.</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Staff member with two-step On</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>1. Super admin: Home Orbit → Staff → Reset two-step
-2. Staff member signs in
-3. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>They sign in with the password only and can set two-step again; the reset is in the audit log.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr"/>
@@ -34499,7 +34596,7 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -34513,12 +34610,12 @@
       <c r="R33" s="11" t="inlineStr"/>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>Super admin, Store staff</t>
+          <t>Store owner, Order manager</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U33" s="11" t="inlineStr">
@@ -34530,7 +34627,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>E2E-11-001</t>
+          <t>E2E-10-002</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -34540,44 +34637,44 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>E2E-11 · Tenant isolation</t>
+          <t>E2E-10 · Staff roles and two-step reset</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Two-step</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Another store's records are invisible</t>
+          <t>Platform resets a staff member's two-step</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Demo Sanitary's owner cannot see Home Orbit data.</t>
+          <t>A vendor staff member who lost their phone is reset by the super admin.</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Both owners signed in</t>
+          <t>Staff member with two-step On</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>A Home Orbit product address</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>1. Demo Sanitary owner: open Products, Categories, Media, Enquiries, Orders
-2. Paste a Home Orbit product's admin address
+          <t>1. Super admin: Home Orbit → Staff → Reset two-step
+2. Staff member signs in
 3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>All lists show only Demo Sanitary's records; the pasted address says it could not be found or no access.</t>
+          <t>They sign in with the password only and can set two-step again; the reset is in the audit log.</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -34588,7 +34685,7 @@
       </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -34602,24 +34699,24 @@
       <c r="R34" s="11" t="inlineStr"/>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>Store owners</t>
+          <t>Super admin, Store staff</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
+          <t>docs/qa/regression/e2e/E2E-10-staff.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>E2E-11-002</t>
+          <t>E2E-11-001</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -34639,34 +34736,34 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Shopper logins are per store</t>
+          <t>Another store's records are invisible</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>A shopper account on one store does not sign in on another.</t>
+          <t>Demo Sanitary's owner cannot see Home Orbit data.</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Shopper account on Home Orbit</t>
+          <t>Both owners signed in</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Same email on demo-sanitary.localhost</t>
+          <t>A Home Orbit product address</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>1. Sign in on Home Orbit
-2. Open http://demo-sanitary.localhost:3000/account
+          <t>1. Demo Sanitary owner: open Products, Categories, Media, Enquiries, Orders
+2. Paste a Home Orbit product's admin address
 3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>Not signed in on Demo Sanitary; the same email there is a separate account.</t>
+          <t>All lists show only Demo Sanitary's records; the pasted address says it could not be found or no access.</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr"/>
@@ -34677,7 +34774,7 @@
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -34691,12 +34788,12 @@
       <c r="R35" s="11" t="inlineStr"/>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Store owners</t>
         </is>
       </c>
       <c r="T35" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U35" s="11" t="inlineStr">
@@ -34708,7 +34805,7 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>E2E-11-003</t>
+          <t>E2E-11-002</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -34728,33 +34825,34 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>API reads are scoped</t>
+          <t>Shopper logins are per store</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>The REST API never returns another store's records.</t>
+          <t>A shopper account on one store does not sign in on another.</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Signed in as Demo Sanitary owner</t>
+          <t>Shopper account on Home Orbit</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>/api/products?limit=5</t>
+          <t>Same email on demo-sanitary.localhost</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>1. Open /api/products?limit=5 in the browser
-2. Verify the expected result.</t>
+          <t>1. Sign in on Home Orbit
+2. Open http://demo-sanitary.localhost:3000/account
+3. Verify the expected result.</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>Only Demo Sanitary's products (or none); never Home Orbit's.</t>
+          <t>Not signed in on Demo Sanitary; the same email there is a separate account.</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -34765,7 +34863,7 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -34779,7 +34877,7 @@
       <c r="R36" s="11" t="inlineStr"/>
       <c r="S36" s="11" t="inlineStr">
         <is>
-          <t>Store owner</t>
+          <t>Shopper</t>
         </is>
       </c>
       <c r="T36" s="11" t="inlineStr">
@@ -34796,7 +34894,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>E2E-12-001</t>
+          <t>E2E-11-003</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -34806,45 +34904,43 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>E2E-12 · Enquiry from store to inbox</t>
+          <t>E2E-11 · Tenant isolation</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Enquiry</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Quote to inbox to closed</t>
+          <t>API reads are scoped</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>A product quote request reaches the inbox and is worked.</t>
+          <t>The REST API never returns another store's records.</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Enquiries on</t>
+          <t>Signed in as Demo Sanitary owner</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Name, 10-digit mobile, city, quantity 50, consent ticked; options picked</t>
+          <t>/api/products?limit=5</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>1. Store: product page → Request a bulk quote with the data
-2. Owner: dashboard figures and bell
-3. Inbox: open it, assign, Contacted, note, Won
-4. Verify the expected result.</t>
+          <t>1. Open /api/products?limit=5 in the browser
+2. Verify the expected result.</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>Store says thanks with ENQ-n; dashboard and bell count it; the inbox shows the options; it moves New → In progress → Closed.</t>
+          <t>Only Demo Sanitary's products (or none); never Home Orbit's.</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -34860,7 +34956,7 @@
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security/Permissions</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr"/>
@@ -34869,155 +34965,245 @@
       <c r="R37" s="11" t="inlineStr"/>
       <c r="S37" s="11" t="inlineStr">
         <is>
-          <t>Shopper, Store owner</t>
+          <t>Store owner</t>
         </is>
       </c>
       <c r="T37" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U37" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
+          <t>docs/qa/regression/e2e/E2E-11-isolation.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
+          <t>E2E-12-001</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>E2E-12 · Enquiry from store to inbox</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Enquiry</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Quote to inbox to closed</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>A product quote request reaches the inbox and is worked.</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Enquiries on</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Name, 10-digit mobile, city, quantity 50, consent ticked; options picked</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>1. Store: product page → Request a bulk quote with the data
+2. Owner: dashboard figures and bell
+3. Inbox: open it, assign, Contacted, note, Won
+4. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Store says thanks with ENQ-n; dashboard and bell count it; the inbox shows the options; it moves New → In progress → Closed.</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr"/>
+      <c r="R38" s="11" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Store owner</t>
+        </is>
+      </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
           <t>E2E-12-002</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>E2E-12 · Enquiry from store to inbox</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Enquiry</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Validation and spam limit</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>The quote form validates and limits repeats.</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>Empty form; then 6 sends in 10 minutes</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>1. Send the form empty
 2. Send a valid form 6 times quickly
 3. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>Errors under Name and consent and "Add a mobile number or an email…"; the 6th send is refused with the wait message.</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr"/>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
+      <c r="M39" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="N39" s="11" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="O38" s="11" t="inlineStr"/>
-      <c r="P38" s="11" t="inlineStr"/>
-      <c r="Q38" s="11" t="inlineStr"/>
-      <c r="R38" s="11" t="inlineStr">
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr"/>
+      <c r="R39" s="11" t="inlineStr">
         <is>
           <t>Also: Boundary</t>
         </is>
       </c>
-      <c r="S38" s="11" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T38" s="11" t="inlineStr">
+      <c r="T39" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U38" s="11" t="inlineStr">
+      <c r="U39" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-12-enquiries.md</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>E2E-13-001</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>E2E-13 · Returns and refunds</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Request, approve, receive, refund</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>A return runs from the shopper to a refund and the report.</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>A delivered order for a shopper account</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>Reason, note, a photo</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>1. Shopper: order page → Request return
 2. Owner: Orders → Returns → Approve with pickup note
@@ -35026,89 +35212,89 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>Shopper sees each state; the return reads Refunded; a credit note lowers the GST summary row.</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr"/>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="M40" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="N40" s="11" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="O39" s="11" t="inlineStr"/>
-      <c r="P39" s="11" t="inlineStr"/>
-      <c r="Q39" s="11" t="inlineStr"/>
-      <c r="R39" s="11" t="inlineStr"/>
-      <c r="S39" s="11" t="inlineStr">
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr"/>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr">
         <is>
           <t>Shopper, Store owner</t>
         </is>
       </c>
-      <c r="T39" s="11" t="inlineStr">
+      <c r="T40" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U39" s="11" t="inlineStr">
+      <c r="U40" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-13-returns.md</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>E2E-14-001</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>E2E-14 · Offer consent, abandoned cart and unsubscribe</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Consent drives reminders; unsubscribe stops offers only</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Offer consent at checkout and unsubscribe behave as promised.</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Offer messages and abandoned cart on</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>Tick "Offers and new launches · By email"</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>1. Shopper: checkout, tick offers by email, leave
 2. After the delay: reminder in the terminal; Return to your cart restores it
@@ -35118,99 +35304,9 @@
 6. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>Reminder sent with consent; after unsubscribe no offer message is sent to that email, but order updates still are.</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="inlineStr"/>
-      <c r="L40" s="11" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M40" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N40" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="O40" s="11" t="inlineStr"/>
-      <c r="P40" s="11" t="inlineStr"/>
-      <c r="Q40" s="11" t="inlineStr"/>
-      <c r="R40" s="11" t="inlineStr"/>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>Shopper, Store owner</t>
-        </is>
-      </c>
-      <c r="T40" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U40" s="11" t="inlineStr">
-        <is>
-          <t>docs/qa/regression/e2e/E2E-14-abandoned.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>E2E-15-001</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>End-to-End</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>E2E-15 · Affiliate referral to commission</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Affiliate</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Referral to approved commission</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>An affiliate link credits the order without exposing the shopper.</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>Approved affiliate</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>/r/&lt;CODE&gt;?to=/products/&lt;slug&gt;</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>1. Open the link in another browser; place a COD order
-2. Affiliate: /affiliate/dashboard
-3. Owner: deliver the order; wait the hold days or run the job
-4. Verify the expected result.</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>Dashboard shows the order "Pending: not delivered yet" without shopper details; after delivery and hold it becomes approved; cancelling reverses it.</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -35221,7 +35317,7 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -35235,7 +35331,7 @@
       <c r="R41" s="11" t="inlineStr"/>
       <c r="S41" s="11" t="inlineStr">
         <is>
-          <t>Affiliate, Shopper, Store owner</t>
+          <t>Shopper, Store owner</t>
         </is>
       </c>
       <c r="T41" s="11" t="inlineStr">
@@ -35245,14 +35341,14 @@
       </c>
       <c r="U41" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-15-affiliate.md</t>
+          <t>docs/qa/regression/e2e/E2E-14-abandoned.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>E2E-16-001</t>
+          <t>E2E-15-001</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -35262,45 +35358,45 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>E2E-16 · Billing to subscriptions</t>
+          <t>E2E-15 · Affiliate referral to commission</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Affiliate</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Payment updates subscriptions and MRR</t>
+          <t>Referral to approved commission</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Recording a vendor payment changes the platform money views.</t>
+          <t>An affiliate link credits the order without exposing the shopper.</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>A trial or past-due vendor</t>
+          <t>Approved affiliate</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>₹9,999</t>
+          <t>/r/&lt;CODE&gt;?to=/products/&lt;slug&gt;</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>1. Super admin: note Subscriptions and dashboard figures
-2. Record a payment on the vendor's Billing
-3. Reload Subscriptions and the dashboard
+          <t>1. Open the link in another browser; place a COD order
+2. Affiliate: /affiliate/dashboard
+3. Owner: deliver the order; wait the hold days or run the job
 4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>The subscription is Active with the new period; Past due and MRR change accordingly.</t>
+          <t>Dashboard shows the order "Pending: not delivered yet" without shopper details; after delivery and hold it becomes approved; cancelling reverses it.</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -35311,7 +35407,7 @@
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
@@ -35325,7 +35421,7 @@
       <c r="R42" s="11" t="inlineStr"/>
       <c r="S42" s="11" t="inlineStr">
         <is>
-          <t>Super admin</t>
+          <t>Affiliate, Shopper, Store owner</t>
         </is>
       </c>
       <c r="T42" s="11" t="inlineStr">
@@ -35335,14 +35431,14 @@
       </c>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-16-billing.md</t>
+          <t>docs/qa/regression/e2e/E2E-15-affiliate.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>E2E-17-001</t>
+          <t>E2E-16-001</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -35352,45 +35448,45 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>E2E-17 · Shopper account and wishlist across devices</t>
+          <t>E2E-16 · Billing to subscriptions</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Guest orders join the account</t>
+          <t>Payment updates subscriptions and MRR</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Logging in with the checkout email shows earlier guest orders.</t>
+          <t>Recording a vendor payment changes the platform money views.</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>A guest COD order with rahul.k@example.com</t>
+          <t>A trial or past-due vendor</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Code from the terminal</t>
+          <t>₹9,999</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>1. Open http://home-orbit.localhost:3000/account → Send code to the email
-2. Type the code from the terminal
-3. Read Your orders
+          <t>1. Super admin: note Subscriptions and dashboard figures
+2. Record a payment on the vendor's Billing
+3. Reload Subscriptions and the dashboard
 4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>My account "Hi Rahul" lists the guest order with Track order and Invoice.</t>
+          <t>The subscription is Active with the new period; Past due and MRR change accordingly.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -35415,7 +35511,7 @@
       <c r="R43" s="11" t="inlineStr"/>
       <c r="S43" s="11" t="inlineStr">
         <is>
-          <t>Shopper</t>
+          <t>Super admin</t>
         </is>
       </c>
       <c r="T43" s="11" t="inlineStr">
@@ -35425,14 +35521,14 @@
       </c>
       <c r="U43" s="11" t="inlineStr">
         <is>
-          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+          <t>docs/qa/regression/e2e/E2E-16-billing.md</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>E2E-17-002</t>
+          <t>E2E-17-001</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -35447,40 +35543,40 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>Account</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Wishlist follows sign-in</t>
+          <t>Guest orders join the account</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>A guest wishlist merges into the account and shows on another browser.</t>
+          <t>Logging in with the checkout email shows earlier guest orders.</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>Wishlist on</t>
+          <t>A guest COD order with rahul.k@example.com</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Code from the terminal</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>1. As a guest tap the heart on two cards
-2. Log in
-3. Open /wishlist in another browser signed in
+          <t>1. Open http://home-orbit.localhost:3000/account → Send code to the email
+2. Type the code from the terminal
+3. Read Your orders
 4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>Both products in the wishlist on both browsers; the header heart shows 2.</t>
+          <t>My account "Hi Rahul" lists the guest order with Track order and Invoice.</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
@@ -35491,12 +35587,12 @@
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="O44" s="11" t="inlineStr"/>
@@ -35522,7 +35618,7 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>E2E-17-003</t>
+          <t>E2E-17-002</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -35537,22 +35633,22 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Log out of all devices</t>
+          <t>Wishlist follows sign-in</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Logging out everywhere ends other sessions.</t>
+          <t>A guest wishlist merges into the account and shows on another browser.</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Signed in on two browsers</t>
+          <t>Wishlist on</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -35562,14 +35658,15 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>1. Press Log out of all devices on one
-2. Open a page on the other
-3. Verify the expected result.</t>
+          <t>1. As a guest tap the heart on two cards
+2. Log in
+3. Open /wishlist in another browser signed in
+4. Verify the expected result.</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>The other browser is signed out on its next page.</t>
+          <t>Both products in the wishlist on both browsers; the header heart shows 2.</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr"/>
@@ -35585,7 +35682,7 @@
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>Security/Permissions</t>
+          <t>Data persistence</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr"/>
@@ -35611,45 +35708,134 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
+          <t>E2E-17-003</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>E2E-17 · Shopper account and wishlist across devices</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>Log out of all devices</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Logging out everywhere ends other sessions.</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Signed in on two browsers</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>1. Press Log out of all devices on one
+2. Open a page on the other
+3. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>The other browser is signed out on its next page.</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr">
+        <is>
+          <t>Security/Permissions</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr"/>
+      <c r="Q46" s="11" t="inlineStr"/>
+      <c r="R46" s="11" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T46" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-17-account.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
           <t>E2E-18-001</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Desktop header icons and menu</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>The desktop header has the menu, search and icons and never overflows.</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Store selling; wishlist on</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>Widths 1280 and 1024</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>1. Open http://home-orbit.localhost:3000 at 1280 px
 2. Read the header
@@ -35657,105 +35843,105 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>Menu items on one line, search box, account, wishlist with count and cart with count; at 1024 the search becomes an icon and nothing overlaps.</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>At 1280 px: menu on one line, search box, account, wishlist and cart icons; at 1024 px the search became an icon and the menu no longer overlapped.</t>
-        </is>
-      </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Menu items on one line, search box, account, wishlist with count and cart with count; at 1024 nothing overlaps (the default header turns the search into an icon; Home Orbit keeps its search bar on its own row).</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>At 1280 px: menu on one line, 547 px search bar, account, wishlist and cart with count; at 1024 px the menu still fits one line, the search bar (367 px) sits on its own row, no overlaps, no sideways scroll.</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M46" s="11" t="inlineStr">
+      <c r="M47" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N46" s="11" t="inlineStr">
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O46" s="11" t="inlineStr">
+      <c r="O47" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P46" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q46" s="11" t="inlineStr"/>
-      <c r="R46" s="11" t="inlineStr">
-        <is>
-          <t>Found and fixed in the same session (search box covered "About us" at 1024 px).</t>
-        </is>
-      </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="P47" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q47" s="11" t="inlineStr"/>
+      <c r="R47" s="11" t="inlineStr">
+        <is>
+          <t>Expected result updated for Home Orbit's header, whose search has its own row.</t>
+        </is>
+      </c>
+      <c r="S47" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T46" s="11" t="inlineStr">
+      <c r="T47" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U46" s="11" t="inlineStr">
+      <c r="U47" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>E2E-18-002</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Bottom navigation</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>The phone bottom bar shows the right tabs and hides on pages with their own bar.</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>Phone size (375 px)</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>1. Read the bottom bar on the home page
 2. Tap Shop
@@ -35763,205 +35949,205 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>Home, Shop, Dealers, Account, Cart; Shop opens /c with all categories; on product, cart and checkout the page's sticky button replaces the bar.</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
-        <is>
-          <t>Phone: bottom bar Home, Shop, Dealers, Account, Cart; Shop opened /c; on a product page the sticky "₹1,049 Add to cart" bar replaced it.</t>
-        </is>
-      </c>
-      <c r="L47" s="11" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>Phone: bottom bar Home, Shop (/c), Dealers, Account, Cart with count; on a product page the sticky "₹849 Add to cart" bar replaces it.</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M47" s="11" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="N48" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q47" s="11" t="inlineStr"/>
-      <c r="R47" s="11" t="inlineStr"/>
-      <c r="S47" s="11" t="inlineStr">
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q48" s="11" t="inlineStr"/>
+      <c r="R48" s="11" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T47" s="11" t="inlineStr">
+      <c r="T48" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U47" s="11" t="inlineStr">
+      <c r="U48" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>E2E-18-003</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Footer columns and legal line</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>The footer matches the wireframe and the store's features.</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Store selling; contact and grievance officer saved (VC-03)</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>1. Scroll to the footer
 2. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>Logo, contact, Get our offers first; Shop with Offers; Help with Track order, published policies, Contact us; Company with Find a dealer and Downloads; legal name, GSTIN, grievance officer and ways to pay.</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
-        <is>
-          <t>Footer: Get our offers first, Shop (with Offers), Help (Track order, Contact us), Company (About us, Contact us, Find a dealer, Downloads), legal line with name and GSTIN, COD chip.</t>
-        </is>
-      </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Footer: Get our offers first; Shop (with Offers); Help (Track order, Privacy policy, Contact us); Company (About us, Contact us, Find a dealer, Downloads); legal line with GSTIN and COD.</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M48" s="11" t="inlineStr">
+      <c r="M49" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N48" s="11" t="inlineStr">
+      <c r="N49" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr">
+      <c r="O49" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P48" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q48" s="11" t="inlineStr"/>
-      <c r="R48" s="11" t="inlineStr">
-        <is>
-          <t>QA data has placeholder business details and no grievance officer or published policies, so those lines were not shown.</t>
-        </is>
-      </c>
-      <c r="S48" s="11" t="inlineStr">
+      <c r="P49" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q49" s="11" t="inlineStr"/>
+      <c r="R49" s="11" t="inlineStr">
+        <is>
+          <t>QA data has placeholder legal name and no grievance officer, so that line was not shown.</t>
+        </is>
+      </c>
+      <c r="S49" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T48" s="11" t="inlineStr">
+      <c r="T49" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U48" s="11" t="inlineStr">
+      <c r="U49" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>E2E-18-004</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Instant search with typos and recent searches</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>Suggestions rank model numbers first and forgive typos.</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>Store with Home Orbit's catalogue</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>"610"; "hogdh610"; "glas handel"</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>1. Type each in the header search
 2. Use arrow keys and Enter
@@ -35969,105 +36155,101 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>HOGDH-610 first for the first two; glass door handles for the typo; Enter opens the choice; Recent searches list earlier terms.</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>"610" and "hogdh610" → HOGDH-610 first; "key" → key hangers and the Key hangers category; "glas handel" → glass door handles (after the swapped-letter fix).</t>
-        </is>
-      </c>
-      <c r="L49" s="11" t="inlineStr">
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>"610" and "hogdh610" → HOGDH-610 first; "glas handel" → glass door handles; ArrowDown + Enter opened HOGDH-610; clearing the box showed Recent searches "hogdh610".</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M49" s="11" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="N50" s="11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O49" s="11" t="inlineStr">
+      <c r="O50" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P49" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q49" s="11" t="inlineStr"/>
-      <c r="R49" s="11" t="inlineStr">
-        <is>
-          <t>Arrow keys and Recent searches were not exercised.</t>
-        </is>
-      </c>
-      <c r="S49" s="11" t="inlineStr">
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q50" s="11" t="inlineStr"/>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T49" s="11" t="inlineStr">
+      <c r="T50" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U49" s="11" t="inlineStr">
+      <c r="U50" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>E2E-18-005</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Listing</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Filter sheet on phones</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>The phone filter sheet works and reports the count.</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Phone size; store selling</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>Price 500–1000</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>1. Open a category
 2. Tap Filter
@@ -36076,101 +36258,101 @@
 5. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>A sheet over a dimmed page with Close and Clear; the count matches the list; Filter (1) after closing.</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>Filter sheet opened over the page with Close, Price, Clear and "Show 50 products"; price 500–1000 gave 21 products, Price low to high cheapest first.</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>Phone: Filter opened a sheet with Close and Clear; max ₹1,000 + Go → "Show 32 products" and 32 in the list (all ≤ ₹1,000); Filter (1) after closing.</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N50" s="11" t="inlineStr">
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="O50" s="11" t="inlineStr">
+      <c r="O51" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P50" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q50" s="11" t="inlineStr"/>
-      <c r="R50" s="11" t="inlineStr"/>
-      <c r="S50" s="11" t="inlineStr">
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q51" s="11" t="inlineStr"/>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T50" s="11" t="inlineStr">
+      <c r="T51" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U50" s="11" t="inlineStr">
+      <c r="U51" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>E2E-18-006</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>End-to-End</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>E2E-18 · Storefront chrome and search (shop experience)</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Move to wishlist and Complete the look</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Cart extras work.</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>Two items in the cart; wishlist on</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>1. Press Move to wishlist on one line
 2. Read Complete the look
@@ -36178,62 +36360,170 @@
 4. Verify the expected result.</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>The line leaves the cart and the heart count goes up; suggestions come from the same categories and Add to cart adds one.</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
-        <is>
-          <t>Move to wishlist removed the door stopper from the cart and the heart read "1 saved"; Complete the look listed 4 products with Add to cart.</t>
-        </is>
-      </c>
-      <c r="L51" s="11" t="inlineStr">
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>Move to wishlist took HOPH-504 out of the cart and the wishlist badge went 0 → 1; Complete the look showed glass door handles; Add to cart on HOGDH-612 made 2 items, ₹1,898.</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="M51" s="11" t="inlineStr">
+      <c r="M52" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N51" s="11" t="inlineStr">
+      <c r="N52" s="11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="O51" s="11" t="inlineStr">
+      <c r="O52" s="11" t="inlineStr">
         <is>
           <t>Claude (in-app browser)</t>
         </is>
       </c>
-      <c r="P51" s="11" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="Q51" s="11" t="inlineStr"/>
-      <c r="R51" s="11" t="inlineStr"/>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="P52" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q52" s="11" t="inlineStr"/>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr">
         <is>
           <t>Shopper</t>
         </is>
       </c>
-      <c r="T51" s="11" t="inlineStr">
+      <c r="T52" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U51" s="11" t="inlineStr">
+      <c r="U52" s="11" t="inlineStr">
         <is>
           <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>E2E-18-007</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>E2E-18 · Storefront chrome and search (shop experience)</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Light animations that respect reduced motion</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>Sections, hero words, menus, quick add and counts move lightly, and stay still for visitors who reduce motion.</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Store selling; a browser with scroll-driven animations (Chrome, Edge)</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Windows: Settings → Accessibility → Visual effects → Animation effects off</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>1. Scroll the home page
+2. Swipe the hero
+3. Open a menu, Quick add, a heart and Add to cart
+4. Turn animations off in the system and reload
+5. Owner: Store settings → Branding → untick Animations on the store, Save; reload the store
+6. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Sections rise in as they arrive, hero words follow their slide, menus and the quick add sheet ease in, the cart and wishlist counts bump; with system animations off everything shows at once and nothing moves (the benefits line stops); with the store switch off the same motion stops for every shopper.</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>Home: sections below the first rise in while scrolling, hero words follow a half-swiped slide (50%); menu dropdown and phone menu ease in; quick add sheet slides up with a fading backdrop; cart and heart bump. Checked with the browser's animation timings. Store switch: with animations off in the store's settings the page carries data-motion="off" and no scroll animations run; the page renders the same. Lighthouse mobile on the production build: accessibility, best practices and SEO 100 on home, listing and product; layout shift 0.</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="O53" s="11" t="inlineStr">
+        <is>
+          <t>Claude (in-app browser)</t>
+        </is>
+      </c>
+      <c r="P53" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q53" s="11" t="inlineStr"/>
+      <c r="R53" s="11" t="inlineStr">
+        <is>
+          <t>Reduced-motion run not done in the in-app browser (it cannot switch the OS setting); the switch was set in the database, not by saving the CMS form (no CMS sign-in in this run).</t>
+        </is>
+      </c>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>Shopper, Store owner</t>
+        </is>
+      </c>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U51"/>
-  <conditionalFormatting sqref="L2:L251">
+  <autoFilter ref="A1:U53"/>
+  <conditionalFormatting sqref="L2:L253">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -36250,25 +36540,25 @@
       <formula>"Not Applicable"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M251">
+  <conditionalFormatting sqref="M2:M253">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="L2:L251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="L2:L253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="M2:M253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="N2:N253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Functional,Regression,Negative,Validation,Boundary,Integration,UI/UX,Security/Permissions,Data persistence,Accessibility"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="B2:B253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Super Admin,Vendor CMS,End-to-End"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="T2:T253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -36282,7 +36572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36501,9 +36791,76 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>DEF-003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>E2E-04-008</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>E2E-04 · Order to cash</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>After placing an order, the same browser could not add anything to the cart: the server rejected every Add to cart until the cart cookie expired (30 days).</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>1. Place an order on the store (E2E-04-001). 2. Open any category. 3. Press Add to cart on a card.</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>The cart count goes to 1.</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Nothing was added; the dev log showed "ValidationError: The following field is invalid: tenant" from saveCart. The ordered cart kept the shopper's cart token, and tokens are unique per store, so the new cart could not be created.</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>Fixed: markCartConverted gives the ordered cart a fresh token, and saveCart frees the token from any older ordered cart before creating a new one (integration test in tests/integration/offers.test.ts). Retested: Add to cart works after an order.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M203"/>
-  <conditionalFormatting sqref="J2:J203">
+  <autoFilter ref="A1:M204"/>
+  <conditionalFormatting sqref="J2:J204">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>
     </cfRule>
@@ -36512,13 +36869,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="F2:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="F2:F204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="J2:J204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Open,In progress,Fixed,Retest,Closed,Won't fix"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="C2:C204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Super Admin,Vendor CMS,End-to-End"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/TenantEcom-test-cases.xlsx
+++ b/docs/qa/TenantEcom-test-cases.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Vendor CMS'!$A$1:$U$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Super Admin'!$A$1:$U$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'End-to-End Workflows'!$A$1:$U$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defect Log'!$A$1:$M$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 from docs/qa/tools. Figures recalculate as Status cells change.</t>
+          <t>Generated 2026-10-14 from docs/qa/tools. Figures recalculate as Status cells change.</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36521,9 +36521,102 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>E2E-18-008</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>End-to-End</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>E2E-18 · Storefront chrome and search (shop experience)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Loaders</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Page loader and busy buttons</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Moving between pages and waiting on a button both show the store’s loader, and a missing page still answers 404.</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Store selling; Chrome DevTools → Network → Slow 4G for the slow steps</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Any product; pincode 560001; /products/no-such-product</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>1. Click a category, then a product (Slow 4G)
+2. Search from the header and press Enter
+3. Add to cart, Buy now and Check the pincode on a product
+4. Place an order (COD)
+5. Turn animations off in the system and repeat one step
+6. Open /products/no-such-product directly
+7. Verify the expected result.</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>A thin bar in the store colour at the top at once; after about half a second the house with a dot circling it and "Loading…" in the middle, gone when the page arrives (quick pages show neither); only the pressed button shows a small ring with its words; the order page loads under the loader; with animations off the ring and dot fade instead of turning; the missing product answers 404 (a moved one still redirects).</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr"/>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>Shopper</t>
+        </is>
+      </c>
+      <c r="T54" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>docs/qa/regression/e2e/E2E-18-storefront.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U53"/>
-  <conditionalFormatting sqref="L2:L253">
+  <autoFilter ref="A1:U54"/>
+  <conditionalFormatting sqref="L2:L254">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -36540,25 +36633,25 @@
       <formula>"Not Applicable"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M253">
+  <conditionalFormatting sqref="M2:M254">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Critical"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="L2:L253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="L2:L254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="M2:M254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="N2:N254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Functional,Regression,Negative,Validation,Boundary,Integration,UI/UX,Security/Permissions,Data persistence,Accessibility"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="B2:B254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Super Admin,Vendor CMS,End-to-End"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
+    <dataValidation sqref="T2:T254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Pick a value from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
